--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Stein (17 ppg)</t>
+          <t>R. Stein (15.5 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein (40 mpg)</t>
+          <t>R. Stein (38.3 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Stein (50.0%)</t>
+          <t>A. Guedes (50.0%)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D. Runge | R. Stein (5 net)</t>
+          <t>M. Drumwright | R. Stein (-2.8 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | R. Stein (5.1 net)</t>
+          <t>M. Drumwright | R. Stein | T. Simao (-4.3 net)</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="41" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -722,67 +722,69 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>55.0%</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>-7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-5.7</v>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -794,77 +796,332 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>38.3%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>45.9%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>D. Runge</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F5" t="n">
+        <v>61</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>62.2%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="F6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>65.2%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>high-minutes, efficient, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U3"/>
+  <autoFilter ref="A1:U6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -875,10 +1132,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -992,10 +1249,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1036,10 +1293,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1080,14 +1337,58 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>K. Warner | M. Drumwright | M. Houge | R. Stein | T. Simao</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1104,7 +1405,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1183,26 +1484,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>D. Runge | R. Stein</t>
+          <t>M. Drumwright | R. Stein</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>70.8</v>
       </c>
       <c r="H2" t="n">
-        <v>83</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>78</v>
+        <v>80.7</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="3">
@@ -1223,26 +1524,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D. Runge | T. Simao</t>
+          <t>D. Runge | M. Drumwright</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>37.9</v>
+        <v>56.2</v>
       </c>
       <c r="H3" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="I3" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4">
@@ -1263,26 +1564,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D. Runge | T. Simao</t>
+          <t>D. Runge | M. Drumwright</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>37.9</v>
+        <v>56.2</v>
       </c>
       <c r="H4" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="I4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5">
@@ -1303,26 +1604,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | R. Stein</t>
+          <t>M. Drumwright | R. Stein | T. Simao</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>55.9</v>
       </c>
       <c r="H5" t="n">
-        <v>85.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>82.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="6">
@@ -1343,26 +1644,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright | R. Stein</t>
+          <t>A. Guedes | D. Runge | M. Drumwright</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>37.9</v>
+        <v>46.7</v>
       </c>
       <c r="H6" t="n">
-        <v>82.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I6" t="n">
-        <v>74</v>
+        <v>72.8</v>
       </c>
       <c r="J6" t="n">
-        <v>8.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="7">
@@ -1383,26 +1684,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright | R. Stein</t>
+          <t>A. Guedes | D. Runge | M. Drumwright</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>37.9</v>
+        <v>46.7</v>
       </c>
       <c r="H7" t="n">
-        <v>82.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I7" t="n">
-        <v>74</v>
+        <v>72.8</v>
       </c>
       <c r="J7" t="n">
-        <v>8.5</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Stein (15.5 ppg)</t>
+          <t>K. Warner (16.5 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein (38.3 mpg)</t>
+          <t>R. Stein (38.0 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Guedes (50.0%)</t>
+          <t>M. Houge (75.0%)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein (-2.8 net)</t>
+          <t>M. Drumwright | R. Stein (-4.9 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein | T. Simao (-4.3 net)</t>
+          <t>M. Drumwright | R. Stein | T. Simao (0 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -722,65 +722,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>76.59999999999999</v>
+        <v>114.1</v>
       </c>
       <c r="G2" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.7</v>
+        <v>-10.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -805,69 +805,69 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>74.3</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>37.1</v>
+        <v>34.3</v>
       </c>
       <c r="H3" t="n">
-        <v>10.5</v>
+        <v>13.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-4.5</v>
+        <v>-6.7</v>
       </c>
       <c r="T3" t="n">
-        <v>39.3</v>
+        <v>37.7</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>high-minutes, primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -888,38 +888,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>64.2</v>
+        <v>93.8</v>
       </c>
       <c r="G4" t="n">
-        <v>32.1</v>
+        <v>31.3</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -939,18 +939,18 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-5.5</v>
+        <v>-6.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.7</v>
+        <v>14.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -962,78 +962,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>61</v>
-      </c>
-      <c r="G5" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
       <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>-15.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>-0.2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, efficient, shooter</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -1045,83 +1045,249 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
       <c r="F6" t="n">
-        <v>55.5</v>
+        <v>70.2</v>
       </c>
       <c r="G6" t="n">
-        <v>27.8</v>
+        <v>23.4</v>
       </c>
       <c r="H6" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>58.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>efficient, shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>53.3%</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>65.2%</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>high-minutes, efficient, shooter</t>
+      <c r="S7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>efficient, shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>52.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-12</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>primary-scorer, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U6"/>
+  <autoFilter ref="A1:U8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1132,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1249,10 +1415,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1293,10 +1459,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1337,10 +1503,10 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1360,35 +1526,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1</v>
+        <v>21.5</v>
       </c>
       <c r="G5" t="n">
-        <v>72.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>112.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-39.8</v>
+        <v>-11.2</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D. Runge | K. Warner | M. Drumwright | R. Stein | T. Simao</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1405,7 +1615,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1488,22 +1698,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>70.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>80.7</v>
+        <v>82.8</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.8</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="3">
@@ -1524,26 +1734,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright</t>
+          <t>D. Runge | R. Stein</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>56.2</v>
+        <v>68.2</v>
       </c>
       <c r="H3" t="n">
-        <v>82.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.7</v>
+        <v>83.3</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -1564,26 +1774,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D. Runge | M. Drumwright</t>
+          <t>M. Drumwright | T. Simao</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>56.2</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>74.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1608,22 +1818,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>55.9</v>
+        <v>73.3</v>
       </c>
       <c r="H5" t="n">
-        <v>77.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I5" t="n">
-        <v>82.2</v>
+        <v>83</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1644,26 +1854,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | M. Drumwright</t>
+          <t>A. Guedes | D. Runge | R. Stein</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>46.7</v>
+        <v>51</v>
       </c>
       <c r="H6" t="n">
-        <v>87.3</v>
+        <v>86.3</v>
       </c>
       <c r="I6" t="n">
-        <v>72.8</v>
+        <v>77.7</v>
       </c>
       <c r="J6" t="n">
-        <v>14.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7">
@@ -1684,26 +1894,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | M. Drumwright</t>
+          <t>A. Guedes | D. Runge | R. Stein</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>46.7</v>
+        <v>51</v>
       </c>
       <c r="H7" t="n">
-        <v>87.3</v>
+        <v>86.3</v>
       </c>
       <c r="I7" t="n">
-        <v>72.8</v>
+        <v>77.7</v>
       </c>
       <c r="J7" t="n">
-        <v>14.6</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_VSC.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Warner (16.5 ppg)</t>
+          <t>R. Stein (16 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein (38.0 mpg)</t>
+          <t>R. Stein (37.5 mpg)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein (-4.9 net)</t>
+          <t>M. Drumwright | R. Stein (2.2 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Drumwright | R. Stein | T. Simao (0 net)</t>
+          <t>M. Drumwright | R. Stein | T. Simao (0.5 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,73 +718,73 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>114.1</v>
+        <v>149.9</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="H2" t="n">
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-10</v>
+        <v>-5.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-10.5</v>
+        <v>17.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, primary-scorer, efficient</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>134.5</v>
       </c>
       <c r="G3" t="n">
-        <v>34.3</v>
+        <v>33.6</v>
       </c>
       <c r="H3" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -846,28 +846,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-6.7</v>
+        <v>-2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>37.7</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, impact</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -888,43 +888,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>93.8</v>
+        <v>110.9</v>
       </c>
       <c r="G4" t="n">
-        <v>31.3</v>
+        <v>27.7</v>
       </c>
       <c r="H4" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,23 +934,23 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="T4" t="n">
-        <v>14.5</v>
+        <v>-3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>high-minutes, shooter</t>
         </is>
       </c>
     </row>
@@ -967,73 +967,73 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>70.8</v>
+        <v>93.2</v>
       </c>
       <c r="G5" t="n">
-        <v>35.4</v>
+        <v>31.1</v>
       </c>
       <c r="H5" t="n">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-15.5</v>
+        <v>-4</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2</v>
+        <v>22.4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -1054,43 +1054,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>70.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1100,23 +1100,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-0.7</v>
+        <v>-2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>26.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>efficient, shooter, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1137,69 +1137,69 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>58.5</v>
+        <v>77.8</v>
       </c>
       <c r="G7" t="n">
         <v>19.5</v>
       </c>
       <c r="H7" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>28.9</v>
+        <v>20.6</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>efficient, shooter, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1216,42 +1216,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>46.1</v>
+        <v>63.1</v>
       </c>
       <c r="G8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>10.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1261,33 +1261,116 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="T8" t="n">
-        <v>-12</v>
+        <v>-20.9</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>primary-scorer, shooter</t>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1298,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1415,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1459,10 +1542,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1503,10 +1586,10 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1547,10 +1630,10 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1566,39 +1649,83 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D. Runge | K. Warner | M. Drumwright | R. Stein | T. Simao</t>
+          <t>K. Warner | M. Drumwright | M. Houge | R. Stein | S. Verde</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="G6" t="n">
-        <v>78.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="H6" t="n">
-        <v>84.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.5</v>
+        <v>-22</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D. Runge | K. Warner | M. Drumwright | R. Stein | T. Simao</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1615,7 +1742,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1698,22 +1825,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>98.59999999999999</v>
+        <v>127.3</v>
       </c>
       <c r="H2" t="n">
-        <v>77.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="I2" t="n">
-        <v>82.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1734,26 +1861,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D. Runge | R. Stein</t>
+          <t>A. Guedes | M. Drumwright</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>68.2</v>
+        <v>64.8</v>
       </c>
       <c r="H3" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>83.3</v>
+        <v>72.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="4">
@@ -1774,26 +1901,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M. Drumwright | T. Simao</t>
+          <t>A. Guedes | M. Drumwright</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>77</v>
+        <v>64.8</v>
       </c>
       <c r="H4" t="n">
-        <v>82.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>81.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="5">
@@ -1818,22 +1945,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>73.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>83</v>
+        <v>81.3</v>
       </c>
       <c r="I5" t="n">
-        <v>83</v>
+        <v>80.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -1854,26 +1981,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | R. Stein</t>
+          <t>A. Guedes | D. Runge | M. Drumwright</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>51</v>
+        <v>49.4</v>
       </c>
       <c r="H6" t="n">
-        <v>86.3</v>
+        <v>84.2</v>
       </c>
       <c r="I6" t="n">
-        <v>77.7</v>
+        <v>74.5</v>
       </c>
       <c r="J6" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1894,26 +2021,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A. Guedes | D. Runge | R. Stein</t>
+          <t>A. Guedes | M. Drumwright | T. Simao</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H7" t="n">
-        <v>86.3</v>
+        <v>81.7</v>
       </c>
       <c r="I7" t="n">
-        <v>77.7</v>
+        <v>72.3</v>
       </c>
       <c r="J7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
